--- a/notebooks/bench_instances/benchmark_log.xlsx
+++ b/notebooks/bench_instances/benchmark_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,24 +578,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N125_M125_T6_seed11_D1.2</t>
+          <t>N400_M400_T6_seed11_D2.0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>center_102_Vicenza_k125.csv</t>
+          <t>center_79_Monza_k400.csv</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>closest_only</t>
+          <t>closest_priority</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>125</v>
+        <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>125</v>
+        <v>400</v>
       </c>
       <c r="F2" t="n">
         <v>6</v>
@@ -604,53 +604,57 @@
         <v>11</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>3059</v>
+        <v>21190</v>
       </c>
       <c r="J2" t="n">
-        <v>0.195776</v>
+        <v>0.1324375</v>
       </c>
       <c r="K2" t="n">
-        <v>751.2291622372677</v>
+        <v>2399.870400061347</v>
       </c>
       <c r="L2" t="n">
-        <v>751.2291622372678</v>
+        <v>1957.770481208789</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0.8157817526974555</v>
       </c>
       <c r="N2" t="n">
-        <v>2.32576025240001</v>
+        <v>7208.545864799991</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>TerminationCondition.optimal</t>
+          <t>TerminationCondition.maxTimeLimit</t>
         </is>
       </c>
       <c r="P2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" t="b">
-        <v>1</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2011.460660013188</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.02692795675777816</v>
+      </c>
       <c r="T2" t="n">
-        <v>747.097255284056</v>
+        <v>1957.803120687222</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9944998049051953</v>
+        <v>0.8157953532145631</v>
       </c>
       <c r="V2" t="n">
-        <v>2001</v>
+        <v>251</v>
       </c>
       <c r="W2" t="n">
         <v>120</v>
       </c>
       <c r="X2" t="n">
-        <v>79.34881329996279</v>
+        <v>121.0516646000033</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -658,39 +662,35 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>4.131906953211796</v>
+        <v>-0.03263947843220194</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.5500195094804875</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>4.131906953211796</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.5500195094804875</v>
-      </c>
+        <v>-0.001667175940463118</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N225_M225_T6_seed11_D1.2</t>
+          <t>N400_M400_T6_seed11_D2.0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>center_58_Trieste_k225.csv</t>
+          <t>center_79_Monza_k400.csv</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>closest_only</t>
+          <t>closest_priority</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>225</v>
+        <v>400</v>
       </c>
       <c r="E3" t="n">
-        <v>225</v>
+        <v>400</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -699,25 +699,25 @@
         <v>11</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>8705</v>
+        <v>21190</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1719506172839506</v>
+        <v>0.1324375</v>
       </c>
       <c r="K3" t="n">
-        <v>1349.613118362984</v>
+        <v>2399.870400061347</v>
       </c>
       <c r="L3" t="n">
-        <v>2.074566933046758</v>
+        <v>1957.770481208789</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001537156763534656</v>
+        <v>0.8157817526974555</v>
       </c>
       <c r="N3" t="n">
-        <v>3.621791848899971</v>
+        <v>7208.545864799991</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -730,22 +730,26 @@
       <c r="Q3" t="b">
         <v>0</v>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+      <c r="R3" t="n">
+        <v>2011.460660013188</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.02692795675777816</v>
+      </c>
       <c r="T3" t="n">
-        <v>1269.98310421201</v>
+        <v>1957.803120687222</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9409978955690936</v>
+        <v>0.8157953532145631</v>
       </c>
       <c r="V3" t="n">
-        <v>1061</v>
+        <v>251</v>
       </c>
       <c r="W3" t="n">
         <v>120</v>
       </c>
       <c r="X3" t="n">
-        <v>120.0575416000211</v>
+        <v>121.0516646000033</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -753,10 +757,10 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>-1267.908537278963</v>
+        <v>-0.03263947843220194</v>
       </c>
       <c r="AA3" t="n">
-        <v>-61116.78139094228</v>
+        <v>-0.001667175940463118</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
@@ -764,24 +768,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N225_M225_T6_seed11_D1.2</t>
+          <t>N400_M400_T6_seed11_D2.0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>center_58_Trieste_k225.csv</t>
+          <t>center_79_Monza_k400.csv</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>closest_only</t>
+          <t>closest_priority</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>225</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>225</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
         <v>6</v>
@@ -790,25 +794,25 @@
         <v>11</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>8705</v>
+        <v>21190</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1719506172839506</v>
+        <v>0.1324375</v>
       </c>
       <c r="K4" t="n">
-        <v>1349.613118362984</v>
+        <v>2399.870400061347</v>
       </c>
       <c r="L4" t="n">
-        <v>2.074566933046758</v>
+        <v>1957.770481208789</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001537156763534656</v>
+        <v>0.8157817526974555</v>
       </c>
       <c r="N4" t="n">
-        <v>5.431150366800022</v>
+        <v>7208.545864799991</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -821,22 +825,26 @@
       <c r="Q4" t="b">
         <v>0</v>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+      <c r="R4" t="n">
+        <v>2011.460660013188</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.02692795675777816</v>
+      </c>
       <c r="T4" t="n">
-        <v>1259.512837929843</v>
+        <v>1957.803120687222</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9332399194945382</v>
+        <v>0.8157953532145631</v>
       </c>
       <c r="V4" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W4" t="n">
         <v>120</v>
       </c>
       <c r="X4" t="n">
-        <v>128.2362726000138</v>
+        <v>121.0516646000033</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -844,10 +852,10 @@
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>-1257.438270996797</v>
+        <v>-0.03263947843220194</v>
       </c>
       <c r="AA4" t="n">
-        <v>-60612.08491114304</v>
+        <v>-0.001667175940463118</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
@@ -855,24 +863,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N225_M225_T6_seed11_D1.2</t>
+          <t>N150_M150_T6_seed11_D2.0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>center_58_Trieste_k225.csv</t>
+          <t>center_4_Bolzano___Bozen_k150.csv</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>closest_only</t>
+          <t>closest_priority</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="E5" t="n">
-        <v>225</v>
+        <v>150</v>
       </c>
       <c r="F5" t="n">
         <v>6</v>
@@ -881,53 +889,57 @@
         <v>11</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>8705</v>
+        <v>11178</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1719506172839506</v>
+        <v>0.4968</v>
       </c>
       <c r="K5" t="n">
-        <v>1349.613118362984</v>
+        <v>901.7344846787157</v>
       </c>
       <c r="L5" t="n">
-        <v>2.074566933046758</v>
+        <v>901.7344846787158</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001537156763534656</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>93.84413446309993</v>
+        <v>479.2124909999839</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>TerminationCondition.maxTimeLimit</t>
+          <t>TerminationCondition.optimal</t>
         </is>
       </c>
       <c r="P5" t="b">
         <v>1</v>
       </c>
       <c r="Q5" t="b">
-        <v>0</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>902.3683384879841</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.23682120168304e-05</v>
+      </c>
       <c r="T5" t="n">
-        <v>1269.98310421201</v>
+        <v>900.1941612610483</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9409978955690936</v>
+        <v>0.9982918215463211</v>
       </c>
       <c r="V5" t="n">
-        <v>1349</v>
+        <v>401</v>
       </c>
       <c r="W5" t="n">
         <v>120</v>
       </c>
       <c r="X5" t="n">
-        <v>120.031322899973</v>
+        <v>106.251814200019</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -935,104 +947,17 @@
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>-1267.908537278963</v>
+        <v>1.540323417667537</v>
       </c>
       <c r="AA5" t="n">
-        <v>-61116.78139094228</v>
-      </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>N225_M225_T6_seed11_D1.2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>center_58_Trieste_k225.csv</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>closest_priority</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>225</v>
-      </c>
-      <c r="E6" t="n">
-        <v>225</v>
-      </c>
-      <c r="F6" t="n">
-        <v>6</v>
-      </c>
-      <c r="G6" t="n">
-        <v>11</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="I6" t="n">
-        <v>8705</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.1719506172839506</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1349.613118362984</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1274.771617897209</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.944545959543907</v>
-      </c>
-      <c r="N6" t="n">
-        <v>6.769680769700091</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>TerminationCondition.maxTimeLimit</t>
-        </is>
-      </c>
-      <c r="P6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q6" t="b">
-        <v>0</v>
-      </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="n">
-        <v>1269.98310421201</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.9409978955690936</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1409</v>
-      </c>
-      <c r="W6" t="n">
-        <v>120</v>
-      </c>
-      <c r="X6" t="n">
-        <v>120.1346208000323</v>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>site_swap,local_remove,area_destroy</t>
-        </is>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.788513685199177</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.3756369861056397</v>
-      </c>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+        <v>0.170817845367902</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.540323417667537</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.170817845367902</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
